--- a/exercise/Admin/Admin Hotel/Tes Excel Admin Hotel 5.xlsx
+++ b/exercise/Admin/Admin Hotel/Tes Excel Admin Hotel 5.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Hotel 5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Hotel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35AA628-9E06-4483-BE4F-BF522EACD24E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -179,7 +178,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -358,6 +357,14 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -367,14 +374,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -662,7 +661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -683,19 +682,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
     </row>
     <row r="2" spans="2:12" s="3" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
@@ -739,19 +738,40 @@
       <c r="C3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="14"/>
+      <c r="D3" s="13" t="str">
+        <f>VLOOKUP(LEFT(B3,3),$B$13:$E$16,2,FALSE)</f>
+        <v>Eksklusif</v>
+      </c>
+      <c r="E3" s="14">
+        <f>VLOOKUP(LEFT(B3,3),$B$13:$E$16,IF(RIGHT(B3,1)="1",3,4),FALSE)</f>
+        <v>550000</v>
+      </c>
       <c r="F3" s="8">
         <v>44685</v>
       </c>
       <c r="G3" s="8">
         <v>44689</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="13"/>
+      <c r="H3" s="13">
+        <f>G3-F3</f>
+        <v>4</v>
+      </c>
+      <c r="I3" s="14">
+        <f>E3*H3</f>
+        <v>2200000</v>
+      </c>
+      <c r="J3" s="14">
+        <f>IF(RIGHT(B3,1)="1",I3*0.05,I3*0.1)</f>
+        <v>110000</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(H3&gt;6,I3*0.02,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="13">
+        <f>I3+J3-K3</f>
+        <v>2310000</v>
+      </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -760,19 +780,40 @@
       <c r="C4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="14"/>
+      <c r="D4" s="13" t="str">
+        <f t="shared" ref="D4:D10" si="0">VLOOKUP(LEFT(B4,3),$B$13:$E$16,2,FALSE)</f>
+        <v>Ekonomi</v>
+      </c>
+      <c r="E4" s="14">
+        <f t="shared" ref="E4:E10" si="1">VLOOKUP(LEFT(B4,3),$B$13:$E$16,IF(RIGHT(B4,1)="1",3,4),FALSE)</f>
+        <v>400000</v>
+      </c>
       <c r="F4" s="8">
         <v>44685</v>
       </c>
       <c r="G4" s="8">
         <v>44693</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="13"/>
+      <c r="H4" s="13">
+        <f t="shared" ref="H4:H10" si="2">G4-F4</f>
+        <v>8</v>
+      </c>
+      <c r="I4" s="14">
+        <f t="shared" ref="I4:I10" si="3">E4*H4</f>
+        <v>3200000</v>
+      </c>
+      <c r="J4" s="14">
+        <f t="shared" ref="J4:J10" si="4">IF(RIGHT(B4,1)="1",I4*0.05,I4*0.1)</f>
+        <v>320000</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K10" si="5">IF(H4&gt;6,I4*0.02,0)</f>
+        <v>64000</v>
+      </c>
+      <c r="L4" s="13">
+        <f t="shared" ref="L4:L10" si="6">I4+J4-K4</f>
+        <v>3456000</v>
+      </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
@@ -781,19 +822,40 @@
       <c r="C5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14"/>
+      <c r="D5" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Luxury</v>
+      </c>
+      <c r="E5" s="14">
+        <f t="shared" si="1"/>
+        <v>600000</v>
+      </c>
       <c r="F5" s="8">
         <v>44684</v>
       </c>
       <c r="G5" s="8">
         <v>44689</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="13"/>
+      <c r="H5" s="13">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="I5" s="14">
+        <f t="shared" si="3"/>
+        <v>3000000</v>
+      </c>
+      <c r="J5" s="14">
+        <f t="shared" si="4"/>
+        <v>150000</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L5" s="13">
+        <f t="shared" si="6"/>
+        <v>3150000</v>
+      </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
@@ -802,19 +864,40 @@
       <c r="C6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14"/>
+      <c r="D6" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Ekonomi</v>
+      </c>
+      <c r="E6" s="14">
+        <f t="shared" si="1"/>
+        <v>400000</v>
+      </c>
       <c r="F6" s="8">
         <v>44698</v>
       </c>
       <c r="G6" s="8">
         <v>44702</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="13"/>
+      <c r="H6" s="13">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="I6" s="14">
+        <f t="shared" si="3"/>
+        <v>1600000</v>
+      </c>
+      <c r="J6" s="14">
+        <f t="shared" si="4"/>
+        <v>160000</v>
+      </c>
+      <c r="K6" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="13">
+        <f t="shared" si="6"/>
+        <v>1760000</v>
+      </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
@@ -823,19 +906,40 @@
       <c r="C7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="14"/>
+      <c r="D7" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Luxury</v>
+      </c>
+      <c r="E7" s="14">
+        <f t="shared" si="1"/>
+        <v>900000</v>
+      </c>
       <c r="F7" s="8">
         <v>44703</v>
       </c>
       <c r="G7" s="8">
         <v>44705</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="13"/>
+      <c r="H7" s="13">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="I7" s="14">
+        <f t="shared" si="3"/>
+        <v>1800000</v>
+      </c>
+      <c r="J7" s="14">
+        <f t="shared" si="4"/>
+        <v>180000</v>
+      </c>
+      <c r="K7" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="13">
+        <f t="shared" si="6"/>
+        <v>1980000</v>
+      </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
@@ -844,19 +948,40 @@
       <c r="C8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14"/>
+      <c r="D8" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Eksklusif</v>
+      </c>
+      <c r="E8" s="14">
+        <f t="shared" si="1"/>
+        <v>550000</v>
+      </c>
       <c r="F8" s="8">
         <v>44690</v>
       </c>
       <c r="G8" s="8">
         <v>44695</v>
       </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="13"/>
+      <c r="H8" s="13">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="I8" s="14">
+        <f t="shared" si="3"/>
+        <v>2750000</v>
+      </c>
+      <c r="J8" s="14">
+        <f t="shared" si="4"/>
+        <v>137500</v>
+      </c>
+      <c r="K8" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="13">
+        <f t="shared" si="6"/>
+        <v>2887500</v>
+      </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
@@ -865,19 +990,40 @@
       <c r="C9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14"/>
+      <c r="D9" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Ekonomi</v>
+      </c>
+      <c r="E9" s="14">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
       <c r="F9" s="8">
         <v>44691</v>
       </c>
       <c r="G9" s="8">
         <v>44696</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="13"/>
+      <c r="H9" s="13">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="I9" s="14">
+        <f t="shared" si="3"/>
+        <v>1500000</v>
+      </c>
+      <c r="J9" s="14">
+        <f t="shared" si="4"/>
+        <v>75000</v>
+      </c>
+      <c r="K9" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="13">
+        <f t="shared" si="6"/>
+        <v>1575000</v>
+      </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
@@ -886,19 +1032,40 @@
       <c r="C10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="14"/>
+      <c r="D10" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Eksklusif</v>
+      </c>
+      <c r="E10" s="14">
+        <f t="shared" si="1"/>
+        <v>650000</v>
+      </c>
       <c r="F10" s="8">
         <v>44692</v>
       </c>
       <c r="G10" s="8">
         <v>44697</v>
       </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="13"/>
+      <c r="H10" s="13">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="I10" s="14">
+        <f t="shared" si="3"/>
+        <v>3250000</v>
+      </c>
+      <c r="J10" s="14">
+        <f t="shared" si="4"/>
+        <v>325000</v>
+      </c>
+      <c r="K10" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="13">
+        <f t="shared" si="6"/>
+        <v>3575000</v>
+      </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H11" s="12"/>
@@ -925,13 +1092,13 @@
       <c r="E13" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
@@ -946,13 +1113,13 @@
       <c r="E14" s="11">
         <v>400000</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
@@ -967,13 +1134,13 @@
       <c r="E15" s="11">
         <v>650000</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
@@ -988,13 +1155,13 @@
       <c r="E16" s="11">
         <v>900000</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C17" s="7"/>
@@ -1004,91 +1171,96 @@
       <c r="E18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="20" t="s">
+      <c r="G18" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="G16:K16"/>
     <mergeCell ref="B23:G23"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="B25:I25"/>
@@ -1097,14 +1269,9 @@
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B21:G21"/>
     <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="G13:K13"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="G15:K15"/>
-    <mergeCell ref="G16:K16"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G18" r:id="rId1" xr:uid="{AB1AC80C-CA7E-4C8C-A6A2-F1F1C14D6EF6}"/>
+    <hyperlink ref="G18" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" r:id="rId2"/>

--- a/exercise/Admin/Admin Hotel/Tes Excel Admin Hotel 5.xlsx
+++ b/exercise/Admin/Admin Hotel/Tes Excel Admin Hotel 5.xlsx
@@ -1,23 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Hotel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6483C1CC-B7F4-4A35-903E-EA2DF90376A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -178,7 +188,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -661,7 +671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -743,7 +753,7 @@
         <v>Eksklusif</v>
       </c>
       <c r="E3" s="14">
-        <f>VLOOKUP(LEFT(B3,3),$B$13:$E$16,IF(RIGHT(B3,1)="1",3,4),FALSE)</f>
+        <f>IF(VALUE(RIGHT(B3,1))=1,VLOOKUP(LEFT(B3,3),$B$13:$E$16,3,FALSE),VLOOKUP(LEFT(B3,3),$B$13:$E$16,4,FALSE))</f>
         <v>550000</v>
       </c>
       <c r="F3" s="8">
@@ -753,7 +763,7 @@
         <v>44689</v>
       </c>
       <c r="H3" s="13">
-        <f>G3-F3</f>
+        <f>_xlfn.DAYS(G3,F3)</f>
         <v>4</v>
       </c>
       <c r="I3" s="14">
@@ -761,11 +771,11 @@
         <v>2200000</v>
       </c>
       <c r="J3" s="14">
-        <f>IF(RIGHT(B3,1)="1",I3*0.05,I3*0.1)</f>
+        <f>IF(VALUE(RIGHT(B3,1))=1,5%*I3,10%*I3)</f>
         <v>110000</v>
       </c>
       <c r="K3" s="14">
-        <f>IF(H3&gt;6,I3*0.02,0)</f>
+        <f>IF(H3&gt;=6,2%*I3,0)</f>
         <v>0</v>
       </c>
       <c r="L3" s="13">
@@ -785,7 +795,7 @@
         <v>Ekonomi</v>
       </c>
       <c r="E4" s="14">
-        <f t="shared" ref="E4:E10" si="1">VLOOKUP(LEFT(B4,3),$B$13:$E$16,IF(RIGHT(B4,1)="1",3,4),FALSE)</f>
+        <f t="shared" ref="E4:E10" si="1">IF(VALUE(RIGHT(B4,1))=1,VLOOKUP(LEFT(B4,3),$B$13:$E$16,3,FALSE),VLOOKUP(LEFT(B4,3),$B$13:$E$16,4,FALSE))</f>
         <v>400000</v>
       </c>
       <c r="F4" s="8">
@@ -795,7 +805,7 @@
         <v>44693</v>
       </c>
       <c r="H4" s="13">
-        <f t="shared" ref="H4:H10" si="2">G4-F4</f>
+        <f t="shared" ref="H4:H10" si="2">_xlfn.DAYS(G4,F4)</f>
         <v>8</v>
       </c>
       <c r="I4" s="14">
@@ -803,11 +813,11 @@
         <v>3200000</v>
       </c>
       <c r="J4" s="14">
-        <f t="shared" ref="J4:J10" si="4">IF(RIGHT(B4,1)="1",I4*0.05,I4*0.1)</f>
+        <f t="shared" ref="J4:J10" si="4">IF(VALUE(RIGHT(B4,1))=1,5%*I4,10%*I4)</f>
         <v>320000</v>
       </c>
       <c r="K4" s="14">
-        <f t="shared" ref="K4:K10" si="5">IF(H4&gt;6,I4*0.02,0)</f>
+        <f t="shared" ref="K4:K10" si="5">IF(H4&gt;=6,2%*I4,0)</f>
         <v>64000</v>
       </c>
       <c r="L4" s="13">
@@ -1271,7 +1281,7 @@
     <mergeCell ref="B22:G22"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G18" r:id="rId1"/>
+    <hyperlink ref="G18" r:id="rId1" xr:uid="{AB1AC80C-CA7E-4C8C-A6A2-F1F1C14D6EF6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" r:id="rId2"/>
